--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,15 +471,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.08</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="C2" t="n">
         <v>70.23999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>72.19</v>
+      </c>
+      <c r="C3" t="n">
+        <v>69.73</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>cnbc.com</t>
         </is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72.19</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>69.73</v>
+        <v>69.97</v>
       </c>
       <c r="D3" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -492,15 +492,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72.40000000000001</v>
+        <v>72.94</v>
       </c>
       <c r="C3" t="n">
-        <v>69.97</v>
+        <v>70.45</v>
       </c>
       <c r="D3" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="E3" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="C4" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>cnbc.com</t>
         </is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -513,18 +513,498 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73.34999999999999</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>70.95</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>cnbc.com</t>
         </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>82.84</v>
+      </c>
+      <c r="C6" t="n">
+        <v>80.43000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>83.62</v>
+      </c>
+      <c r="C7" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>82.16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>79.45999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>88.87</v>
+      </c>
+      <c r="C9" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="C10" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>82.37</v>
+      </c>
+      <c r="C11" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="C12" t="n">
+        <v>73.68000000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>88.23</v>
+      </c>
+      <c r="C13" t="n">
+        <v>84.09</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>72.03</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>82.59</v>
+      </c>
+      <c r="C16" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>79.51000000000001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>75.01000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>84.95</v>
+      </c>
+      <c r="C19" t="n">
+        <v>81.26000000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>81.22</v>
+      </c>
+      <c r="C20" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>75.86</v>
+      </c>
+      <c r="C21" t="n">
+        <v>73.68000000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>76.23999999999999</v>
+      </c>
+      <c r="C22" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>81.22</v>
+      </c>
+      <c r="C23" t="n">
+        <v>77.97</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="C24" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>75.68000000000001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>77.76000000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>88.91</v>
+      </c>
+      <c r="C28" t="n">
+        <v>85.42</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>86.06</v>
+      </c>
+      <c r="C29" t="n">
+        <v>81.84</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>81.83</v>
+      </c>
+      <c r="C30" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>83.26000000000001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>79.63</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>83.34</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>78.65000000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>74.33</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>84.59</v>
+      </c>
+      <c r="C34" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.18</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1007,6 +1007,27 @@
         <v>2.18</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>72.39</v>
+      </c>
+      <c r="C35" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>72.39</v>
+        <v>72.38</v>
       </c>
       <c r="C35" t="n">
-        <v>68.97</v>
+        <v>69.02</v>
       </c>
       <c r="D35" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>72.38</v>
+        <v>72.11</v>
       </c>
       <c r="C35" t="n">
-        <v>69.02</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>3.36</v>
+        <v>3.21</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1014,15 +1014,57 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>72.11</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>68.90000000000001</v>
+        <v>68.38</v>
       </c>
       <c r="D35" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="E35" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>70.67</v>
+      </c>
+      <c r="C36" t="n">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>72.01000000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>68.77</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>cnbc.com</t>
         </is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>72.01000000000001</v>
+        <v>71.44</v>
       </c>
       <c r="C37" t="n">
-        <v>68.77</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1056,15 +1056,36 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>71.44</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>68.31999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="D37" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="E37" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="C38" t="n">
+        <v>68.78</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>cnbc.com</t>
         </is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1091,6 +1091,27 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="C39" t="n">
+        <v>68.78</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1112,6 +1112,48 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="C40" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="C41" t="n">
+        <v>68.79000000000001</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1140,15 +1140,36 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>71.98999999999999</v>
+        <v>73.83</v>
       </c>
       <c r="C41" t="n">
-        <v>68.79000000000001</v>
+        <v>70.31</v>
       </c>
       <c r="D41" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="E41" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="C42" t="n">
+        <v>74.69</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>cnbc.com</t>
         </is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1161,15 +1161,36 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>79.08</v>
+        <v>79.67</v>
       </c>
       <c r="C42" t="n">
-        <v>74.69</v>
+        <v>75.39</v>
       </c>
       <c r="D42" t="n">
-        <v>4.39</v>
+        <v>4.28</v>
       </c>
       <c r="E42" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>78.02</v>
+      </c>
+      <c r="C43" t="n">
+        <v>74.45</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>cnbc.com</t>
         </is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1182,15 +1182,36 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>78.02</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>74.45</v>
+        <v>72.87</v>
       </c>
       <c r="D43" t="n">
-        <v>3.57</v>
+        <v>4.06</v>
       </c>
       <c r="E43" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="C44" t="n">
+        <v>71.86</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>cnbc.com</t>
         </is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -1203,13 +1203,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>76.09999999999999</v>
+        <v>76.28</v>
       </c>
       <c r="C44" t="n">
-        <v>71.86</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>4.24</v>
+        <v>4.38</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1203,15 +1203,78 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>76.28</v>
+        <v>76.3</v>
       </c>
       <c r="C44" t="n">
-        <v>71.90000000000001</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>4.38</v>
+        <v>4.48</v>
       </c>
       <c r="E44" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>76.01000000000001</v>
+      </c>
+      <c r="C45" t="n">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>76.01000000000001</v>
+      </c>
+      <c r="C46" t="n">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>78.64</v>
+      </c>
+      <c r="C47" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>cnbc.com</t>
         </is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1266,15 +1266,57 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>78.64</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>73.95</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>4.69</v>
+        <v>4.2</v>
       </c>
       <c r="E47" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>84</v>
+      </c>
+      <c r="C48" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="D48" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>84.84999999999999</v>
+      </c>
+      <c r="C49" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>cnbc.com</t>
         </is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1308,15 +1308,183 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>84.84999999999999</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="C49" t="n">
-        <v>79.68000000000001</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
       <c r="E49" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>84.87</v>
+      </c>
+      <c r="C50" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>86.66</v>
+      </c>
+      <c r="C51" t="n">
+        <v>81.39</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="C52" t="n">
+        <v>82.47</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="C53" t="n">
+        <v>82.47</v>
+      </c>
+      <c r="D53" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>88.15000000000001</v>
+      </c>
+      <c r="C54" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="D54" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>91.34</v>
+      </c>
+      <c r="C55" t="n">
+        <v>85.23999999999999</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>93.94</v>
+      </c>
+      <c r="C56" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="D56" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>94.06999999999999</v>
+      </c>
+      <c r="C57" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="D57" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>cnbc.com</t>
         </is>

--- a/data/harga_minyak.xlsx
+++ b/data/harga_minyak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
